--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_2_3.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_2_3.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-47015.50734382177</v>
+        <v>-62389.55346936799</v>
       </c>
     </row>
     <row r="7">
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="C4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="D4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="E4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="F4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="G4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="H4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="I4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="J4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="K4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="L4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="M4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="N4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="O4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
       <c r="P4" t="n">
-        <v>10750.74055314464</v>
+        <v>12588.27138056849</v>
       </c>
     </row>
     <row r="5">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-28252.22972342768</v>
+        <v>-30089.76055085153</v>
       </c>
       <c r="C6" t="n">
-        <v>-28252.22972342768</v>
+        <v>-30089.76055085153</v>
       </c>
       <c r="D6" t="n">
-        <v>-28252.22972342768</v>
+        <v>-30089.76055085153</v>
       </c>
       <c r="E6" t="n">
-        <v>5375.370276572316</v>
+        <v>3537.839449148465</v>
       </c>
       <c r="F6" t="n">
-        <v>5375.370276572316</v>
+        <v>3537.839449148465</v>
       </c>
       <c r="G6" t="n">
-        <v>5375.370276572316</v>
+        <v>3537.839449148465</v>
       </c>
       <c r="H6" t="n">
-        <v>5375.370276572316</v>
+        <v>3537.839449148465</v>
       </c>
       <c r="I6" t="n">
-        <v>5375.370276572317</v>
+        <v>3537.839449148465</v>
       </c>
       <c r="J6" t="n">
-        <v>5375.370276572316</v>
+        <v>3537.839449148465</v>
       </c>
       <c r="K6" t="n">
-        <v>5375.370276572316</v>
+        <v>3537.839449148465</v>
       </c>
       <c r="L6" t="n">
-        <v>5375.370276572317</v>
+        <v>3537.839449148467</v>
       </c>
       <c r="M6" t="n">
-        <v>5375.370276572317</v>
+        <v>3537.839449148465</v>
       </c>
       <c r="N6" t="n">
-        <v>5375.370276572316</v>
+        <v>3537.839449148465</v>
       </c>
       <c r="O6" t="n">
-        <v>5375.370276572316</v>
+        <v>3537.839449148467</v>
       </c>
       <c r="P6" t="n">
-        <v>5375.370276572316</v>
+        <v>3537.839449148465</v>
       </c>
     </row>
   </sheetData>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,34 +26892,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26928,13 +26928,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
